--- a/examples/blank_template.xlsx
+++ b/examples/blank_template.xlsx
@@ -1296,7 +1296,7 @@
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>Generated by Investment-Grade Company Analysis Engine v1.0 on 18 Jun 2026. Illustrative analytical tool — not investment advice.</t>
+          <t>Generated by Investment-Grade Company Analysis Engine v1.0 on 22 Jun 2026. Illustrative analytical tool — not investment advice.</t>
         </is>
       </c>
     </row>
